--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>10157 INCA GARCILAZO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.539828</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-80.012604</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1449</v>
-      </c>
-      <c r="J2" t="n">
-        <v>48</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.539828</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-80.012604</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>10165 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.493233</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.939009</v>
-      </c>
-      <c r="I3" t="n">
-        <v>777</v>
-      </c>
-      <c r="J3" t="n">
-        <v>44</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.493233</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.939009</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>10169 SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.539942</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.942465</v>
-      </c>
-      <c r="I4" t="n">
-        <v>571</v>
-      </c>
-      <c r="J4" t="n">
-        <v>27</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.539942</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.942465</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>10159 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.4812</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.9515</v>
-      </c>
-      <c r="I5" t="n">
-        <v>236</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.4812</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.9515</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>11066 SEGUNDO MANUEL RUIZ SANCHEZ</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.4852</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.96259999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>263</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.4852</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.9626</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>11078 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.516837</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-80.00343100000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>213</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.516837</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-80.003431</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>11079</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.511506</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.954317</v>
-      </c>
-      <c r="I8" t="n">
-        <v>226</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.511506</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.954317</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>11080 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.46572</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.95867699999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>254</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.46572</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.958677</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>10940 SAN ISIDRO LABRADOR</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.62616</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.95837</v>
-      </c>
-      <c r="I10" t="n">
-        <v>432</v>
-      </c>
-      <c r="J10" t="n">
-        <v>26</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.62616</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.95837</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>10159 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.48066</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.95124</v>
-      </c>
-      <c r="I11" t="n">
-        <v>233</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.48066</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.95124</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>10161 JOSE FAUSTINO SANCHEZ CARRIO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.48884</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.99885</v>
-      </c>
-      <c r="I12" t="n">
-        <v>403</v>
-      </c>
-      <c r="J12" t="n">
-        <v>22</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.48884</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.99885</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>343 LEON TOLSTOI</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.5402</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-80.01691</v>
-      </c>
-      <c r="I13" t="n">
-        <v>229</v>
-      </c>
-      <c r="J13" t="n">
-        <v>9</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.5402</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-80.01691</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>CIENCIA COLLEGE</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.539557</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-80.01369</v>
-      </c>
-      <c r="I14" t="n">
-        <v>421</v>
-      </c>
-      <c r="J14" t="n">
-        <v>23</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.539557</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-80.01369</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>11572 - MOCHICA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-6.611161</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.96582600000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>552</v>
-      </c>
-      <c r="J15" t="n">
-        <v>27</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.611161</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.965826</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>10157 INCA GARCILAZO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-6.540304</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-80.012636</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1168</v>
-      </c>
-      <c r="J16" t="n">
-        <v>49</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-6.540304</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.012636</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1168</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,22 +1439,156 @@
           <t>212 CARMELITAS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-6.5407</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-80.0129</v>
-      </c>
-      <c r="I17" t="n">
-        <v>364</v>
-      </c>
-      <c r="J17" t="n">
-        <v>13</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-6.5407</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-80.0129</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>140306</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MORROPE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>284796</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10162</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-6.49647</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.94518</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>140306</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MORROPE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>284961</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>11053 RICARDO PALMA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-6.494017</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.96711</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>284739</t>
+          <t>285003</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10157 INCA GARCILAZO DE LA VEGA</t>
+          <t>11079</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.539828</t>
+          <t>-6.511506</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.012604</t>
+          <t>-79.954317</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>284744</t>
+          <t>284999</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10165 MIGUEL GRAU SEMINARIO</t>
+          <t>11078 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.493233</t>
+          <t>-6.516837</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.939009</t>
+          <t>-80.003431</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>284800</t>
+          <t>284824</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10169 SEÑOR DE LA DIVINA MISERICORDIA</t>
+          <t>10159 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.539942</t>
+          <t>-6.4812</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.942465</t>
+          <t>-79.9515</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>284824</t>
+          <t>678557</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10159 DANIEL ALCIDES CARRION</t>
+          <t>212 CARMELITAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.4812</t>
+          <t>-6.5407</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.9515</t>
+          <t>-80.0129</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>364</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,27 +749,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>284980</t>
+          <t>284937</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11066 SEGUNDO MANUEL RUIZ SANCHEZ</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.4852</t>
+          <t>-6.499594</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.9626</t>
+          <t>-79.955264</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>284999</t>
+          <t>284980</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11078 FRANCISCO BOLOGNESI</t>
+          <t>11066 SEGUNDO MANUEL RUIZ SANCHEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.516837</t>
+          <t>-6.4852</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.003431</t>
+          <t>-79.9626</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>285003</t>
+          <t>516230</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>10159 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.511506</t>
+          <t>-6.48066</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.954317</t>
+          <t>-79.95124</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>285183</t>
+          <t>516249</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10940 SAN ISIDRO LABRADOR</t>
+          <t>10161 JOSE FAUSTINO SANCHEZ CARRIO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.62616</t>
+          <t>-6.48884</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.95837</t>
+          <t>-79.99885</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>516230</t>
+          <t>860434</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10159 DANIEL ALCIDES CARRION</t>
+          <t>11624 MARTIR PNP WILLIAMS WILFREDO VALDIVIESO SANTA MARIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.48066</t>
+          <t>-6.54789</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.95124</t>
+          <t>-80.01769</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>487</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>516249</t>
+          <t>638547</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10161 JOSE FAUSTINO SANCHEZ CARRIO</t>
+          <t>CIENCIA COLLEGE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.48884</t>
+          <t>-6.539557</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.99885</t>
+          <t>-80.01369</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>421</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>635308</t>
+          <t>285183</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>343 LEON TOLSTOI</t>
+          <t>10940 SAN ISIDRO LABRADOR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.5402</t>
+          <t>-6.62616</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.01691</t>
+          <t>-79.95837</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>638547</t>
+          <t>284800</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CIENCIA COLLEGE</t>
+          <t>10169 SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.539557</t>
+          <t>-6.539942</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.01369</t>
+          <t>-79.942465</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>571</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>678538</t>
+          <t>284720</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10157 INCA GARCILAZO DE LA VEGA</t>
+          <t>10160 ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.540304</t>
+          <t>-6.509</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.012636</t>
+          <t>-79.9649</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>809</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>678557</t>
+          <t>284744</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>212 CARMELITAS</t>
+          <t>10165 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.5407</t>
+          <t>-6.493233</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.0129</t>
+          <t>-79.939009</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>777</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>284796</t>
+          <t>284739</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10157 INCA GARCILAZO DE LA VEGA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.49647</t>
+          <t>-6.539828</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.94518</t>
+          <t>-80.012604</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,40 +1555,226 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>678538</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10157 INCA GARCILAZO DE LA VEGA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-6.540304</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-80.012636</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1168</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>140306</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MORROPE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>635308</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>343 LEON TOLSTOI</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-6.5402</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-80.01691</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>140306</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MORROPE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>284796</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10162</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-6.49647</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.94518</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>140306</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MORROPE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>284961</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>11053 RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>-6.494017</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>-79.96711</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>285003</t>
+          <t>860434</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>11624 MARTIR PNP WILLIAMS WILFREDO VALDIVIESO SANTA MARIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.511506</t>
+          <t>487</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.954317</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-6.54789</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-80.01769</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>284999</t>
+          <t>678557</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11078 FRANCISCO BOLOGNESI</t>
+          <t>212 CARMELITAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.516837</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.003431</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-6.5407</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.0129</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>284824</t>
+          <t>678538</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10159 DANIEL ALCIDES CARRION</t>
+          <t>10157 INCA GARCILAZO DE LA VEGA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.4812</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.9515</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-6.540304</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-80.012636</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>678557</t>
+          <t>678406</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>212 CARMELITAS</t>
+          <t>11572 - MOCHICA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.5407</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.0129</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>-6.611161</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.965826</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>284937</t>
+          <t>638547</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>CIENCIA COLLEGE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.499594</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.955264</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-6.539557</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.01369</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>284980</t>
+          <t>635308</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11066 SEGUNDO MANUEL RUIZ SANCHEZ</t>
+          <t>343 LEON TOLSTOI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.4852</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.9626</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-6.5402</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.01691</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>516230</t>
+          <t>516249</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10159 DANIEL ALCIDES CARRION</t>
+          <t>10161 JOSE FAUSTINO SANCHEZ CARRIO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.48066</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.95124</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-6.48884</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.99885</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>285164</t>
+          <t>516230</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11080 JORGE CHAVEZ DARTNELL</t>
+          <t>10159 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.46572</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.958677</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-6.48066</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.95124</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>516249</t>
+          <t>285183</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10161 JOSE FAUSTINO SANCHEZ CARRIO</t>
+          <t>10940 SAN ISIDRO LABRADOR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.48884</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.99885</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-6.62616</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.95837</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>860434</t>
+          <t>285164</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11624 MARTIR PNP WILLIAMS WILFREDO VALDIVIESO SANTA MARIA</t>
+          <t>11080 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.54789</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.01769</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>-6.46572</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.958677</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>638547</t>
+          <t>285003</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CIENCIA COLLEGE</t>
+          <t>11079</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.539557</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.01369</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-6.511506</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.954317</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>285183</t>
+          <t>284999</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10940 SAN ISIDRO LABRADOR</t>
+          <t>11078 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.62616</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.95837</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-6.516837</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.003431</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>284800</t>
+          <t>284980</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10169 SEÑOR DE LA DIVINA MISERICORDIA</t>
+          <t>11066 SEGUNDO MANUEL RUIZ SANCHEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.539942</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.942465</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>-6.4852</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.9626</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>678406</t>
+          <t>284961</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11572 - MOCHICA</t>
+          <t>11053 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.611161</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.965826</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>-6.494017</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.96711</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>284720</t>
+          <t>284937</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10160 ROSA DE AMERICA</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.509</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.9649</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>-6.499594</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-79.955264</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>284744</t>
+          <t>284824</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10165 MIGUEL GRAU SEMINARIO</t>
+          <t>10159 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.493233</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.939009</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>-6.4812</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-79.9515</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>284739</t>
+          <t>284800</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10157 INCA GARCILAZO DE LA VEGA</t>
+          <t>10169 SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.539828</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.012604</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>-6.539942</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-79.942465</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>678538</t>
+          <t>284796</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10157 INCA GARCILAZO DE LA VEGA</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.540304</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.012636</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>-6.49647</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-79.94518</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>635308</t>
+          <t>284744</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>343 LEON TOLSTOI</t>
+          <t>10165 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.5402</t>
+          <t>777</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.01691</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-6.493233</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.939009</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>284796</t>
+          <t>284739</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10157 INCA GARCILAZO DE LA VEGA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.49647</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.94518</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>-6.539828</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-80.012604</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>284961</t>
+          <t>284720</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>11053 RICARDO PALMA</t>
+          <t>10160 ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.494017</t>
+          <t>809</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.96711</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>-6.509</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.9649</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">

--- a/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-LAMBAYEQUE-MORROPE.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
